--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/IndonesiaEPS/Shared Documents/Updated Indonesia InputData files/elec/RQSD/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\elec\RQSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_623A52F21C17C819F46193B58750562F6094C7BB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45652FCD-8769-4B39-9E81-9D06B3E8294E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB127EA-7A1A-41B8-83CC-AD09D724D06C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30030" yWindow="2355" windowWidth="19200" windowHeight="11205" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -614,109 +614,112 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE25"/>
+  <dimension ref="A1:AF25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.453125" customWidth="1"/>
-    <col min="2" max="2" width="28.453125" customWidth="1"/>
+    <col min="2" max="3" width="28.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B1" s="3">
+        <v>2020</v>
+      </c>
+      <c r="C1" s="3">
         <v>2021</v>
       </c>
-      <c r="C1" s="3">
+      <c r="D1" s="3">
         <v>2022</v>
       </c>
-      <c r="D1" s="3">
+      <c r="E1" s="3">
         <v>2023</v>
       </c>
-      <c r="E1" s="3">
+      <c r="F1" s="3">
         <v>2024</v>
       </c>
-      <c r="F1" s="3">
+      <c r="G1" s="3">
         <v>2025</v>
       </c>
-      <c r="G1" s="3">
+      <c r="H1" s="3">
         <v>2026</v>
       </c>
-      <c r="H1" s="3">
+      <c r="I1" s="3">
         <v>2027</v>
       </c>
-      <c r="I1" s="3">
+      <c r="J1" s="3">
         <v>2028</v>
       </c>
-      <c r="J1" s="3">
+      <c r="K1" s="3">
         <v>2029</v>
       </c>
-      <c r="K1" s="3">
+      <c r="L1" s="3">
         <v>2030</v>
       </c>
-      <c r="L1" s="3">
+      <c r="M1" s="3">
         <v>2031</v>
       </c>
-      <c r="M1" s="3">
+      <c r="N1" s="3">
         <v>2032</v>
       </c>
-      <c r="N1" s="3">
+      <c r="O1" s="3">
         <v>2033</v>
       </c>
-      <c r="O1" s="3">
+      <c r="P1" s="3">
         <v>2034</v>
       </c>
-      <c r="P1" s="3">
+      <c r="Q1" s="3">
         <v>2035</v>
       </c>
-      <c r="Q1" s="3">
+      <c r="R1" s="3">
         <v>2036</v>
       </c>
-      <c r="R1" s="3">
+      <c r="S1" s="3">
         <v>2037</v>
       </c>
-      <c r="S1" s="3">
+      <c r="T1" s="3">
         <v>2038</v>
       </c>
-      <c r="T1" s="3">
+      <c r="U1" s="3">
         <v>2039</v>
       </c>
-      <c r="U1" s="3">
+      <c r="V1" s="3">
         <v>2040</v>
       </c>
-      <c r="V1" s="3">
+      <c r="W1" s="3">
         <v>2041</v>
       </c>
-      <c r="W1" s="3">
+      <c r="X1" s="3">
         <v>2042</v>
       </c>
-      <c r="X1" s="3">
+      <c r="Y1" s="3">
         <v>2043</v>
       </c>
-      <c r="Y1" s="3">
+      <c r="Z1" s="3">
         <v>2044</v>
       </c>
-      <c r="Z1" s="3">
+      <c r="AA1" s="3">
         <v>2045</v>
       </c>
-      <c r="AA1" s="3">
+      <c r="AB1" s="3">
         <v>2046</v>
       </c>
-      <c r="AB1" s="3">
+      <c r="AC1" s="3">
         <v>2047</v>
       </c>
-      <c r="AC1" s="3">
+      <c r="AD1" s="3">
         <v>2048</v>
       </c>
-      <c r="AD1" s="3">
+      <c r="AE1" s="3">
         <v>2049</v>
       </c>
-      <c r="AE1" s="3">
+      <c r="AF1" s="3">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -810,8 +813,11 @@
       <c r="AE2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -905,8 +911,11 @@
       <c r="AE3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -1000,8 +1009,11 @@
       <c r="AE4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -1095,8 +1107,11 @@
       <c r="AE5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1190,8 +1205,11 @@
       <c r="AE6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1285,8 +1303,11 @@
       <c r="AE7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1380,8 +1401,11 @@
       <c r="AE8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -1475,8 +1499,11 @@
       <c r="AE9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1570,8 +1597,11 @@
       <c r="AE10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -1665,8 +1695,11 @@
       <c r="AE11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -1760,8 +1793,11 @@
       <c r="AE12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1855,8 +1891,11 @@
       <c r="AE13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1865,11 +1904,11 @@
         <v>0</v>
       </c>
       <c r="C14">
-        <f t="shared" ref="C14:AE14" si="0">C2</f>
+        <f>C2</f>
         <v>0</v>
       </c>
       <c r="D14">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D14:AF14" si="0">D2</f>
         <v>0</v>
       </c>
       <c r="E14">
@@ -1980,8 +2019,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -2075,8 +2118,11 @@
       <c r="AE15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -2170,8 +2216,11 @@
       <c r="AE16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -2265,8 +2314,11 @@
       <c r="AE17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -2360,8 +2412,11 @@
       <c r="AE18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -2455,8 +2510,11 @@
       <c r="AE19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -2550,8 +2608,11 @@
       <c r="AE20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -2645,8 +2706,11 @@
       <c r="AE21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -2740,8 +2804,11 @@
       <c r="AE22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -2835,8 +2902,11 @@
       <c r="AE23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>37</v>
       </c>
@@ -2930,8 +3000,11 @@
       <c r="AE24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>38</v>
       </c>
@@ -3023,6 +3096,9 @@
         <v>1</v>
       </c>
       <c r="AE25">
+        <v>1</v>
+      </c>
+      <c r="AF25">
         <v>1</v>
       </c>
     </row>
@@ -3036,109 +3112,112 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE25"/>
+  <dimension ref="A1:AF25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.453125" customWidth="1"/>
-    <col min="2" max="2" width="28.453125" customWidth="1"/>
+    <col min="2" max="3" width="28.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B1" s="3">
+        <v>2020</v>
+      </c>
+      <c r="C1" s="3">
         <v>2021</v>
       </c>
-      <c r="C1" s="3">
+      <c r="D1" s="3">
         <v>2022</v>
       </c>
-      <c r="D1" s="3">
+      <c r="E1" s="3">
         <v>2023</v>
       </c>
-      <c r="E1" s="3">
+      <c r="F1" s="3">
         <v>2024</v>
       </c>
-      <c r="F1" s="3">
+      <c r="G1" s="3">
         <v>2025</v>
       </c>
-      <c r="G1" s="3">
+      <c r="H1" s="3">
         <v>2026</v>
       </c>
-      <c r="H1" s="3">
+      <c r="I1" s="3">
         <v>2027</v>
       </c>
-      <c r="I1" s="3">
+      <c r="J1" s="3">
         <v>2028</v>
       </c>
-      <c r="J1" s="3">
+      <c r="K1" s="3">
         <v>2029</v>
       </c>
-      <c r="K1" s="3">
+      <c r="L1" s="3">
         <v>2030</v>
       </c>
-      <c r="L1" s="3">
+      <c r="M1" s="3">
         <v>2031</v>
       </c>
-      <c r="M1" s="3">
+      <c r="N1" s="3">
         <v>2032</v>
       </c>
-      <c r="N1" s="3">
+      <c r="O1" s="3">
         <v>2033</v>
       </c>
-      <c r="O1" s="3">
+      <c r="P1" s="3">
         <v>2034</v>
       </c>
-      <c r="P1" s="3">
+      <c r="Q1" s="3">
         <v>2035</v>
       </c>
-      <c r="Q1" s="3">
+      <c r="R1" s="3">
         <v>2036</v>
       </c>
-      <c r="R1" s="3">
+      <c r="S1" s="3">
         <v>2037</v>
       </c>
-      <c r="S1" s="3">
+      <c r="T1" s="3">
         <v>2038</v>
       </c>
-      <c r="T1" s="3">
+      <c r="U1" s="3">
         <v>2039</v>
       </c>
-      <c r="U1" s="3">
+      <c r="V1" s="3">
         <v>2040</v>
       </c>
-      <c r="V1" s="3">
+      <c r="W1" s="3">
         <v>2041</v>
       </c>
-      <c r="W1" s="3">
+      <c r="X1" s="3">
         <v>2042</v>
       </c>
-      <c r="X1" s="3">
+      <c r="Y1" s="3">
         <v>2043</v>
       </c>
-      <c r="Y1" s="3">
+      <c r="Z1" s="3">
         <v>2044</v>
       </c>
-      <c r="Z1" s="3">
+      <c r="AA1" s="3">
         <v>2045</v>
       </c>
-      <c r="AA1" s="3">
+      <c r="AB1" s="3">
         <v>2046</v>
       </c>
-      <c r="AB1" s="3">
+      <c r="AC1" s="3">
         <v>2047</v>
       </c>
-      <c r="AC1" s="3">
+      <c r="AD1" s="3">
         <v>2048</v>
       </c>
-      <c r="AD1" s="3">
+      <c r="AE1" s="3">
         <v>2049</v>
       </c>
-      <c r="AE1" s="3">
+      <c r="AF1" s="3">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -3232,8 +3311,11 @@
       <c r="AE2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -3327,8 +3409,11 @@
       <c r="AE3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -3422,8 +3507,11 @@
       <c r="AE4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -3517,8 +3605,11 @@
       <c r="AE5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3612,8 +3703,11 @@
       <c r="AE6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -3707,8 +3801,11 @@
       <c r="AE7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -3802,8 +3899,11 @@
       <c r="AE8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -3897,8 +3997,11 @@
       <c r="AE9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -3992,8 +4095,11 @@
       <c r="AE10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -4087,8 +4193,11 @@
       <c r="AE11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -4182,8 +4291,11 @@
       <c r="AE12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -4277,8 +4389,11 @@
       <c r="AE13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -4287,11 +4402,11 @@
         <v>0</v>
       </c>
       <c r="C14">
-        <f t="shared" ref="C14:AE14" si="0">C2</f>
+        <f>C2</f>
         <v>0</v>
       </c>
       <c r="D14">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D14:AF14" si="0">D2</f>
         <v>0</v>
       </c>
       <c r="E14">
@@ -4402,8 +4517,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -4497,8 +4616,11 @@
       <c r="AE15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -4592,8 +4714,11 @@
       <c r="AE16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -4687,8 +4812,11 @@
       <c r="AE17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -4782,8 +4910,11 @@
       <c r="AE18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -4877,8 +5008,11 @@
       <c r="AE19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -4972,8 +5106,11 @@
       <c r="AE20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -5067,8 +5204,11 @@
       <c r="AE21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -5162,8 +5302,11 @@
       <c r="AE22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -5257,8 +5400,11 @@
       <c r="AE23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>37</v>
       </c>
@@ -5352,8 +5498,11 @@
       <c r="AE24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="AF24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>38</v>
       </c>
@@ -5445,6 +5594,9 @@
         <v>1</v>
       </c>
       <c r="AE25">
+        <v>1</v>
+      </c>
+      <c r="AF25">
         <v>1</v>
       </c>
     </row>
@@ -5454,21 +5606,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
     <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
@@ -5612,24 +5749,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4D2CB83-6E6E-4C39-A7E1-290DD52A535B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADF4CFF9-64F4-4637-8C70-1C52A7372417}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D275AD2-80BA-44D5-9D98-26D118E3BD21}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5645,4 +5780,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADF4CFF9-64F4-4637-8C70-1C52A7372417}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4D2CB83-6E6E-4C39-A7E1-290DD52A535B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>